--- a/VerveStacks_KEN_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_KEN_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02B7E4D6-F984-4285-A39B-DA0EC8445CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C44F3E95-F167-44B3-9B22-4912425EFD7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2329,7 +2329,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{511FF911-8750-4568-904D-6554957BB7CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C05E385-A9B1-4C95-9725-B3904DD3F65E}">
   <dimension ref="B2:AF279"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7134,7 +7134,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68D3EC22-F7B3-45E8-B039-F96603A3A12D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB4C0E5D-E06C-41CF-842E-7AE7335F59ED}">
   <dimension ref="B9:L26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18454,7 +18454,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EE7399A-44AB-462A-B674-052B86EA6984}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3D3232A-2E96-4A79-BB75-F563E0B8268D}">
   <dimension ref="A1:I65"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
